--- a/scalability evaluation/input samples/sample_1.xlsx
+++ b/scalability evaluation/input samples/sample_1.xlsx
@@ -442,11 +442,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6084</v>
+        <v>1624</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q55902846</t>
+          <t>Q115043621</t>
         </is>
       </c>
     </row>
